--- a/artfynd/A 60449-2022 artfynd.xlsx
+++ b/artfynd/A 60449-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136125881</v>
       </c>
       <c r="B2" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60449-2022 artfynd.xlsx
+++ b/artfynd/A 60449-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136125881</v>
       </c>
       <c r="B2" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60449-2022 artfynd.xlsx
+++ b/artfynd/A 60449-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136125881</v>
       </c>
       <c r="B2" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
